--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/04_Finanzierung_Sicherheiten/07_CP_Checkliste_und_Ziehungsregister.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/04_Finanzierung_Sicherheiten/07_CP_Checkliste_und_Ziehungsregister.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CP_Nachweise" sheetId="1" r:id="R70d2f251db4b4bf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ziehungen" sheetId="2" r:id="R665d2136baf743d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrollsummen" sheetId="3" r:id="R69d853b4874c4676"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CP_Nachweise" sheetId="1" r:id="R7aabb1be7b5e44c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ziehungen" sheetId="2" r:id="R39049f766d7c480a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrollsummen" sheetId="3" r:id="R85120995cdac4f71"/>
   </x:sheets>
 </x:workbook>
 </file>
